--- a/Data/Commodore 128/310378/Data C128 310378.xlsx
+++ b/Data/Commodore 128/310378/Data C128 310378.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Development\Visual Studio\Commodore-Repair-Toolbox\Data\Commodore 128\310378\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3BC958-AADB-4971-A01F-3DDE55FA23C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DF92F0-15C5-482F-A933-F3AF8D5D858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17425" uniqueCount="3397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17426" uniqueCount="3398">
   <si>
     <t>Name</t>
   </si>
@@ -10436,8 +10436,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-February-21</t>
+      <t>2026-March-7</t>
     </r>
+  </si>
+  <si>
+    <t>2026-March-7</t>
   </si>
 </sst>
 </file>
@@ -11320,7 +11323,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{421B51B2-79EE-4420-A06F-4DB0AB134ADC}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="83.5546875" customWidth="1"/>
@@ -11369,6 +11372,11 @@
     <row r="11" spans="1:1">
       <c r="A11" t="s">
         <v>3395</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>3397</v>
       </c>
     </row>
   </sheetData>
